--- a/internal_doc/03.开发设计/mysql/MySQL 类型转换兼容性与转换规则.xlsx
+++ b/internal_doc/03.开发设计/mysql/MySQL 类型转换兼容性与转换规则.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linsuqiang\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\trunk\internal_doc\03.开发设计\mysql\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="405">
   <si>
     <t>BOOL</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -282,10 +282,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>小范围转大范围必然成功。大范围转小范围时，如果超出小范围边界，则取最大值（最小值）。超出精度时四舍五入。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>小范围转大范围必然成功。大范围转小范围时，如果超出小范围边界，则取最大值（最小值）。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -650,14 +646,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>如果是20XX，则转为XX（0&lt;XX&lt;100）。其余直接转为对应数字。特殊地，0000转为9999。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>转为对应整数，再将整数转字符串。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>转为对应整数，再将整数转二进制。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -826,10 +814,6 @@
   </si>
   <si>
     <t>DATETIME=&gt;DATETIME</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>转为TIMESTAMP，再截取DATE。除非是零值，否则必然有数据截断警告。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1247,10 +1231,6 @@
   </si>
   <si>
     <t>TIMESTAMP=&gt;DATETIME</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1 byte。范围 1901~2155。特殊地，有零值0000。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1542,10 +1522,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>增加元素则无需更新。如删除原元素，则剔除被删除的元素。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>最多拥有 65535 个枚举值。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1566,10 +1542,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>如果数值超出BIT范围，则将数值截取为该BIT能显示的最大数值范围。如BIT(3)，截取后为7。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>必然警告。置全零。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1586,14 +1558,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>轻量级的必然兼容的转换。无需更新操作。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>必然兼容的转换。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>可能不兼容的转换。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1607,6 +1571,211 @@
   </si>
   <si>
     <t>MySQL 类型转换兼容性总览</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SSQL-MySQL 处理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DECIMAL=&gt;DECIMAL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小范围转大范围必然成功。大范围转小范围时，如果超出小范围边界，则取最大值（最小值）。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果数值超出BIT范围，则置为该BIT能显示的最大数值范围。如BIT(3)，置为7。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>依赖 MySQL 方法，逐条更新。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SSQL-MySQL 类型转换处理策略总览</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>依赖 SDB 方法更新</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>依赖 MySQL 方法逐条更新</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无需更新</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>必然兼容的转换。L字母表示转换是轻量的，无需更新的。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>依赖 sdb $cast 方法。cast 需支持设置异常处理值。</t>
+  </si>
+  <si>
+    <t>依赖 sdb $cast 方法。cast 需支持转 DECIMAL 时指定精度。</t>
+  </si>
+  <si>
+    <t>依赖 sdb $cast 方法。</t>
+  </si>
+  <si>
+    <t>依赖 sdb $cast 方法。cast 需支持设置异常处理值，和 DECIMAL 指定精度。</t>
+  </si>
+  <si>
+    <t>依赖 sdb $cast 或用 set 更新。如果 BIT 位数正好是 8 的整数倍，则使用 sdb $cast 方法。否则，更新超出范围的值为该BIT表示的最大值。</t>
+  </si>
+  <si>
+    <t>用 sdb $set 更新。将超出范围的数值更新为 0。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用 sdb $set 更新。全部更新为空JSON。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>依赖 sdb $substr 方法。</t>
+  </si>
+  <si>
+    <t>依赖 sdb $cast 方法。cast 需支持 TINYINT, INT UNSIGNED 等隐藏类型。需支持 DECIMAL 指定精度。</t>
+  </si>
+  <si>
+    <t>依赖 sdb $cast 方法和 $substr 方法和 $truncate 方法。cast 需支持 BINARY 类型。</t>
+  </si>
+  <si>
+    <t>依赖 sdb $cast 方法。先 cast 为 Int64 然后按数值转 BIT 规则处理。最好 sdb update 支持流式处理。</t>
+  </si>
+  <si>
+    <t>依赖 sdb $cast 方法。但 cast 时总是使用 utf8 字符集。</t>
+  </si>
+  <si>
+    <t>依赖 sdb $cast 方法。cast 为 String 然后按字符串转 BIT 规则处理。</t>
+  </si>
+  <si>
+    <t>依赖 sdb $cast 方法。sdb 实现 BINARY 转 DATE 时规则与 MySQL 对齐即可。</t>
+  </si>
+  <si>
+    <t>依赖 sdb $cast 方法。sdb 实现 BINARY 转 TIMESTAMP 时规则与 MySQL 对齐即可。</t>
+  </si>
+  <si>
+    <t>依赖 sdb $truncate 方法。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>依赖 sdb $cast 方法和 $substr 方法。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>依赖 sdb $cast 方法和 $truncate 方法。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用 sdb $set 更新，将超范围的值均置为 BIT 能表示的最大值。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>依赖 MySQL 方法，逐条更新。</t>
+  </si>
+  <si>
+    <t>依赖 sdb $cast 方法。源类型根据 BIT 位数取最接近的一个数值类型。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>依赖 sdb $cast 方法。源类型取 Int32。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>依赖 sdb $cast 方法或用 $set 更新。等于 INT 转 BIT。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>转为对应整数，再将整数转字符串。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>直接转为对应数字。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无需操作。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>依赖 sdb $cast 方法。源类型取 Double。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>转为DATETIME，再截取DATE。除非是零值，否则必然有数据截断警告。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用 sdb $set 更新。将超出范围的数值更新为 0。有小数位的属于超范围。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>依赖 sdb $cast 方法。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用 sdb $set 更新。全部置为 0000。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用 sdb $set 更新。全部置零值00:00:00。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>依赖 sdb $substr 方法。一般无需操作。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>依赖 sdb $cast 方法。但时间部分是零值也一样会有警告。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>依赖 MySQL 方法，逐条更新。不能使用 sdb 的 $cast，因为无法解决精度问题。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>依赖 sdb $cast 方法。源类型为大小最近接的整数类型。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>先转字符串，然后从字符串转新定义。增加元素则无需更新。如删除原元素，则剔除被删除的元素。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用 sdb $set 更新。全部更新为零值。</t>
+  </si>
+  <si>
+    <t>用 sdb $set 更新。全部更新为零值。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1 byte。范围 1901~2155。特殊地，有零值0000。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>依赖 sdb $cast 和 $substr 方法。cast 需支持设置异常处理值，DECIMAL 指定精度。最好支持更新的流式处理。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>依赖 sdb $cast 和 $substr 方法和 $truncate 方法。cast 需支持设置异常处理值，DECIMAL 指定精度，支持 BINARY 类型。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>依赖 sdb $cast 方法。cast 需支持按字面转换。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>依赖 sdb $cast 方法。cast 需支持设置有效数值范围。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>依赖 sdb $cast 方法。支持指定 TIMESTAMP 毫微秒精度。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1662,7 +1831,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1690,6 +1859,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1723,7 +1910,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1767,6 +1954,27 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2057,7 +2265,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AJ37"/>
+  <dimension ref="A1:AJ73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.75" style="2" customWidth="1"/>
@@ -2067,174 +2275,217 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" ht="38.25" customHeight="1">
-      <c r="A1" s="15" t="s">
-        <v>358</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
-      <c r="S1" s="15"/>
-      <c r="T1" s="15"/>
-      <c r="U1" s="15"/>
-      <c r="V1" s="15"/>
-      <c r="W1" s="15"/>
-      <c r="X1" s="15"/>
-      <c r="Y1" s="15"/>
-      <c r="Z1" s="15"/>
-      <c r="AA1" s="15"/>
-      <c r="AB1" s="15"/>
-      <c r="AC1" s="15"/>
-      <c r="AD1" s="15"/>
-      <c r="AE1" s="15"/>
+      <c r="A1" s="22" t="s">
+        <v>349</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
+      <c r="V1" s="22"/>
+      <c r="W1" s="22"/>
+      <c r="X1" s="22"/>
+      <c r="Y1" s="22"/>
+      <c r="Z1" s="22"/>
+      <c r="AA1" s="22"/>
+      <c r="AB1" s="22"/>
+      <c r="AC1" s="22"/>
+      <c r="AD1" s="22"/>
+      <c r="AE1" s="22"/>
     </row>
     <row r="2" spans="1:36">
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="3" spans="1:36">
+      <c r="B3" s="6"/>
+      <c r="C3" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="4" spans="1:36">
+      <c r="B4" s="11"/>
+      <c r="C4" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="5" spans="1:36">
+      <c r="B5" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="6" spans="1:36" ht="89.25" customHeight="1">
+      <c r="A6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="T6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="U6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="V6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="W6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="X6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC6" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="AD6" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="AE6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF6" s="4"/>
+      <c r="AG6" s="4"/>
+      <c r="AH6" s="4"/>
+      <c r="AI6" s="4"/>
+      <c r="AJ6" s="4"/>
+    </row>
+    <row r="7" spans="1:36">
+      <c r="A7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="3" spans="1:36">
-      <c r="B3" s="5"/>
-      <c r="C3" s="2" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="4" spans="1:36">
-      <c r="B4" s="6"/>
-      <c r="C4" s="2" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="5" spans="1:36">
-      <c r="B5" s="11"/>
-      <c r="C5" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="6" spans="1:36">
-      <c r="B6" s="2" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="7" spans="1:36" ht="89.25" customHeight="1">
-      <c r="A7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="P7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="R7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="S7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="T7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="U7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="V7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="W7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="X7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC7" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="AD7" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="AE7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="AF7" s="4"/>
-      <c r="AG7" s="4"/>
-      <c r="AH7" s="4"/>
-      <c r="AI7" s="4"/>
-      <c r="AJ7" s="4"/>
+      <c r="C7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="9"/>
+      <c r="S7" s="10"/>
+      <c r="T7" s="8"/>
+      <c r="U7" s="8"/>
+      <c r="V7" s="8"/>
+      <c r="W7" s="6"/>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="6"/>
+      <c r="Z7" s="6"/>
+      <c r="AA7" s="6"/>
+      <c r="AB7" s="6"/>
+      <c r="AC7" s="6"/>
+      <c r="AD7" s="6"/>
+      <c r="AE7" s="11"/>
     </row>
     <row r="8" spans="1:36">
       <c r="A8" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>30</v>
@@ -2255,10 +2506,10 @@
         <v>30</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J8" s="9"/>
       <c r="K8" s="9"/>
@@ -2285,14 +2536,10 @@
     </row>
     <row r="9" spans="1:36">
       <c r="A9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>30</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
       <c r="D9" s="8" t="s">
         <v>30</v>
       </c>
@@ -2306,10 +2553,10 @@
         <v>30</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J9" s="9"/>
       <c r="K9" s="9"/>
@@ -2336,13 +2583,11 @@
     </row>
     <row r="10" spans="1:36">
       <c r="A10" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
-      <c r="D10" s="8" t="s">
-        <v>30</v>
-      </c>
+      <c r="D10" s="6"/>
       <c r="E10" s="8" t="s">
         <v>30</v>
       </c>
@@ -2352,11 +2597,9 @@
       <c r="G10" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="H10" s="8" t="s">
-        <v>66</v>
-      </c>
+      <c r="H10" s="8"/>
       <c r="I10" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J10" s="9"/>
       <c r="K10" s="9"/>
@@ -2383,14 +2626,12 @@
     </row>
     <row r="11" spans="1:36">
       <c r="A11" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
-      <c r="E11" s="8" t="s">
-        <v>30</v>
-      </c>
+      <c r="E11" s="6"/>
       <c r="F11" s="8" t="s">
         <v>30</v>
       </c>
@@ -2399,7 +2640,7 @@
       </c>
       <c r="H11" s="8"/>
       <c r="I11" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J11" s="9"/>
       <c r="K11" s="9"/>
@@ -2426,22 +2667,18 @@
     </row>
     <row r="12" spans="1:36">
       <c r="A12" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
-      <c r="F12" s="8" t="s">
-        <v>30</v>
-      </c>
+      <c r="F12" s="6"/>
       <c r="G12" s="8" t="s">
         <v>30</v>
       </c>
       <c r="H12" s="8"/>
-      <c r="I12" s="8" t="s">
-        <v>66</v>
-      </c>
+      <c r="I12" s="8"/>
       <c r="J12" s="9"/>
       <c r="K12" s="9"/>
       <c r="L12" s="9"/>
@@ -2467,18 +2704,20 @@
     </row>
     <row r="13" spans="1:36">
       <c r="A13" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
-      <c r="G13" s="8" t="s">
+      <c r="G13" s="6"/>
+      <c r="H13" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
+      <c r="I13" s="8" t="s">
+        <v>30</v>
+      </c>
       <c r="J13" s="9"/>
       <c r="K13" s="9"/>
       <c r="L13" s="9"/>
@@ -2489,9 +2728,9 @@
       <c r="Q13" s="9"/>
       <c r="R13" s="9"/>
       <c r="S13" s="10"/>
-      <c r="T13" s="8"/>
-      <c r="U13" s="8"/>
-      <c r="V13" s="8"/>
+      <c r="T13" s="10"/>
+      <c r="U13" s="10"/>
+      <c r="V13" s="10"/>
       <c r="W13" s="6"/>
       <c r="X13" s="6"/>
       <c r="Y13" s="6"/>
@@ -2504,7 +2743,7 @@
     </row>
     <row r="14" spans="1:36">
       <c r="A14" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -2512,9 +2751,7 @@
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
-      <c r="H14" s="8" t="s">
-        <v>30</v>
-      </c>
+      <c r="H14" s="6"/>
       <c r="I14" s="8" t="s">
         <v>30</v>
       </c>
@@ -2543,18 +2780,16 @@
     </row>
     <row r="15" spans="1:36">
       <c r="A15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="8" t="s">
-        <v>30</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
       <c r="J15" s="9"/>
       <c r="K15" s="9"/>
       <c r="L15" s="9"/>
@@ -2580,7 +2815,7 @@
     </row>
     <row r="16" spans="1:36">
       <c r="A16" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -2593,10 +2828,18 @@
       <c r="J16" s="9"/>
       <c r="K16" s="9"/>
       <c r="L16" s="9"/>
-      <c r="M16" s="8"/>
-      <c r="N16" s="8"/>
-      <c r="O16" s="8"/>
-      <c r="P16" s="8"/>
+      <c r="M16" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="N16" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="O16" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="P16" s="8" t="s">
+        <v>65</v>
+      </c>
       <c r="Q16" s="9"/>
       <c r="R16" s="9"/>
       <c r="S16" s="10"/>
@@ -2611,11 +2854,11 @@
       <c r="AB16" s="6"/>
       <c r="AC16" s="6"/>
       <c r="AD16" s="6"/>
-      <c r="AE16" s="11"/>
+      <c r="AE16" s="6"/>
     </row>
     <row r="17" spans="1:31">
       <c r="A17" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -2629,16 +2872,16 @@
       <c r="K17" s="9"/>
       <c r="L17" s="9"/>
       <c r="M17" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N17" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O17" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P17" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Q17" s="9"/>
       <c r="R17" s="9"/>
@@ -2658,7 +2901,7 @@
     </row>
     <row r="18" spans="1:31">
       <c r="A18" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -2672,16 +2915,16 @@
       <c r="K18" s="9"/>
       <c r="L18" s="9"/>
       <c r="M18" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N18" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O18" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P18" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Q18" s="9"/>
       <c r="R18" s="9"/>
@@ -2701,7 +2944,7 @@
     </row>
     <row r="19" spans="1:31">
       <c r="A19" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -2714,17 +2957,15 @@
       <c r="J19" s="9"/>
       <c r="K19" s="9"/>
       <c r="L19" s="9"/>
-      <c r="M19" s="8" t="s">
-        <v>66</v>
-      </c>
+      <c r="M19" s="9"/>
       <c r="N19" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O19" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P19" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Q19" s="9"/>
       <c r="R19" s="9"/>
@@ -2744,7 +2985,7 @@
     </row>
     <row r="20" spans="1:31">
       <c r="A20" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -2758,14 +2999,12 @@
       <c r="K20" s="9"/>
       <c r="L20" s="9"/>
       <c r="M20" s="9"/>
-      <c r="N20" s="8" t="s">
-        <v>66</v>
-      </c>
+      <c r="N20" s="9"/>
       <c r="O20" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P20" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Q20" s="9"/>
       <c r="R20" s="9"/>
@@ -2785,7 +3024,7 @@
     </row>
     <row r="21" spans="1:31">
       <c r="A21" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
@@ -2800,11 +3039,9 @@
       <c r="L21" s="9"/>
       <c r="M21" s="9"/>
       <c r="N21" s="9"/>
-      <c r="O21" s="8" t="s">
-        <v>66</v>
-      </c>
+      <c r="O21" s="9"/>
       <c r="P21" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Q21" s="9"/>
       <c r="R21" s="9"/>
@@ -2824,7 +3061,7 @@
     </row>
     <row r="22" spans="1:31">
       <c r="A22" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
@@ -2837,18 +3074,24 @@
       <c r="J22" s="9"/>
       <c r="K22" s="9"/>
       <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
-      <c r="P22" s="8" t="s">
-        <v>66</v>
-      </c>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="8"/>
       <c r="Q22" s="9"/>
       <c r="R22" s="9"/>
-      <c r="S22" s="10"/>
-      <c r="T22" s="10"/>
-      <c r="U22" s="10"/>
-      <c r="V22" s="10"/>
+      <c r="S22" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="T22" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="U22" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="V22" s="8" t="s">
+        <v>65</v>
+      </c>
       <c r="W22" s="6"/>
       <c r="X22" s="6"/>
       <c r="Y22" s="6"/>
@@ -2861,7 +3104,7 @@
     </row>
     <row r="23" spans="1:31">
       <c r="A23" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
@@ -2881,16 +3124,16 @@
       <c r="Q23" s="9"/>
       <c r="R23" s="9"/>
       <c r="S23" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T23" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="U23" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="V23" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="W23" s="6"/>
       <c r="X23" s="6"/>
@@ -2904,7 +3147,7 @@
     </row>
     <row r="24" spans="1:31">
       <c r="A24" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
@@ -2924,16 +3167,16 @@
       <c r="Q24" s="9"/>
       <c r="R24" s="9"/>
       <c r="S24" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T24" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="U24" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="V24" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="W24" s="6"/>
       <c r="X24" s="6"/>
@@ -2947,7 +3190,7 @@
     </row>
     <row r="25" spans="1:31">
       <c r="A25" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -2966,17 +3209,15 @@
       <c r="P25" s="8"/>
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
-      <c r="S25" s="8" t="s">
-        <v>66</v>
-      </c>
+      <c r="S25" s="9"/>
       <c r="T25" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="U25" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="V25" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="W25" s="6"/>
       <c r="X25" s="6"/>
@@ -2990,7 +3231,7 @@
     </row>
     <row r="26" spans="1:31">
       <c r="A26" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
@@ -3010,14 +3251,12 @@
       <c r="Q26" s="9"/>
       <c r="R26" s="9"/>
       <c r="S26" s="9"/>
-      <c r="T26" s="8" t="s">
-        <v>66</v>
-      </c>
+      <c r="T26" s="9"/>
       <c r="U26" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="V26" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="W26" s="6"/>
       <c r="X26" s="6"/>
@@ -3031,7 +3270,7 @@
     </row>
     <row r="27" spans="1:31">
       <c r="A27" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B27" s="9"/>
       <c r="C27" s="9"/>
@@ -3052,11 +3291,9 @@
       <c r="R27" s="9"/>
       <c r="S27" s="9"/>
       <c r="T27" s="9"/>
-      <c r="U27" s="8" t="s">
-        <v>66</v>
-      </c>
+      <c r="U27" s="9"/>
       <c r="V27" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="W27" s="6"/>
       <c r="X27" s="6"/>
@@ -3070,16 +3307,18 @@
     </row>
     <row r="28" spans="1:31">
       <c r="A28" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
+      <c r="G28" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
       <c r="J28" s="9"/>
       <c r="K28" s="9"/>
       <c r="L28" s="9"/>
@@ -3089,12 +3328,10 @@
       <c r="P28" s="8"/>
       <c r="Q28" s="9"/>
       <c r="R28" s="9"/>
-      <c r="S28" s="9"/>
-      <c r="T28" s="9"/>
-      <c r="U28" s="9"/>
-      <c r="V28" s="8" t="s">
-        <v>66</v>
-      </c>
+      <c r="S28" s="10"/>
+      <c r="T28" s="8"/>
+      <c r="U28" s="8"/>
+      <c r="V28" s="8"/>
       <c r="W28" s="6"/>
       <c r="X28" s="6"/>
       <c r="Y28" s="6"/>
@@ -3103,20 +3340,18 @@
       <c r="AB28" s="6"/>
       <c r="AC28" s="6"/>
       <c r="AD28" s="6"/>
-      <c r="AE28" s="6"/>
+      <c r="AE28" s="11"/>
     </row>
     <row r="29" spans="1:31">
       <c r="A29" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="8" t="s">
-        <v>30</v>
-      </c>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
       <c r="H29" s="8"/>
       <c r="I29" s="8"/>
       <c r="J29" s="9"/>
@@ -3133,7 +3368,9 @@
       <c r="U29" s="8"/>
       <c r="V29" s="8"/>
       <c r="W29" s="6"/>
-      <c r="X29" s="6"/>
+      <c r="X29" s="8" t="s">
+        <v>65</v>
+      </c>
       <c r="Y29" s="6"/>
       <c r="Z29" s="6"/>
       <c r="AA29" s="6"/>
@@ -3144,16 +3381,18 @@
     </row>
     <row r="30" spans="1:31">
       <c r="A30" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="8" t="s">
+        <v>30</v>
+      </c>
       <c r="J30" s="9"/>
       <c r="K30" s="9"/>
       <c r="L30" s="9"/>
@@ -3168,11 +3407,9 @@
       <c r="U30" s="8"/>
       <c r="V30" s="8"/>
       <c r="W30" s="6"/>
-      <c r="X30" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y30" s="6"/>
-      <c r="Z30" s="6"/>
+      <c r="X30" s="6"/>
+      <c r="Y30" s="8"/>
+      <c r="Z30" s="11"/>
       <c r="AA30" s="6"/>
       <c r="AB30" s="6"/>
       <c r="AC30" s="6"/>
@@ -3181,18 +3418,16 @@
     </row>
     <row r="31" spans="1:31">
       <c r="A31" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
       <c r="H31" s="9"/>
-      <c r="I31" s="8" t="s">
-        <v>30</v>
-      </c>
+      <c r="I31" s="8"/>
       <c r="J31" s="9"/>
       <c r="K31" s="9"/>
       <c r="L31" s="9"/>
@@ -3208,9 +3443,11 @@
       <c r="V31" s="8"/>
       <c r="W31" s="6"/>
       <c r="X31" s="6"/>
-      <c r="Y31" s="8"/>
-      <c r="Z31" s="11"/>
-      <c r="AA31" s="6"/>
+      <c r="Y31" s="6"/>
+      <c r="Z31" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA31" s="8"/>
       <c r="AB31" s="6"/>
       <c r="AC31" s="6"/>
       <c r="AD31" s="6"/>
@@ -3218,14 +3455,14 @@
     </row>
     <row r="32" spans="1:31">
       <c r="A32" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
       <c r="H32" s="9"/>
       <c r="I32" s="8"/>
       <c r="J32" s="9"/>
@@ -3243,10 +3480,8 @@
       <c r="V32" s="8"/>
       <c r="W32" s="6"/>
       <c r="X32" s="6"/>
-      <c r="Y32" s="6"/>
-      <c r="Z32" s="8" t="s">
-        <v>66</v>
-      </c>
+      <c r="Y32" s="8"/>
+      <c r="Z32" s="6"/>
       <c r="AA32" s="8"/>
       <c r="AB32" s="6"/>
       <c r="AC32" s="6"/>
@@ -3255,7 +3490,7 @@
     </row>
     <row r="33" spans="1:31">
       <c r="A33" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
@@ -3283,23 +3518,23 @@
       <c r="Y33" s="8"/>
       <c r="Z33" s="6"/>
       <c r="AA33" s="8"/>
-      <c r="AB33" s="6"/>
+      <c r="AB33" s="8"/>
       <c r="AC33" s="6"/>
       <c r="AD33" s="6"/>
       <c r="AE33" s="11"/>
     </row>
     <row r="34" spans="1:31">
       <c r="A34" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
+      <c r="G34" s="8"/>
       <c r="H34" s="9"/>
-      <c r="I34" s="8"/>
+      <c r="I34" s="9"/>
       <c r="J34" s="9"/>
       <c r="K34" s="9"/>
       <c r="L34" s="9"/>
@@ -3315,26 +3550,26 @@
       <c r="V34" s="8"/>
       <c r="W34" s="6"/>
       <c r="X34" s="6"/>
-      <c r="Y34" s="8"/>
+      <c r="Y34" s="6"/>
       <c r="Z34" s="6"/>
-      <c r="AA34" s="8"/>
-      <c r="AB34" s="8"/>
+      <c r="AA34" s="6"/>
+      <c r="AB34" s="6"/>
       <c r="AC34" s="6"/>
       <c r="AD34" s="6"/>
-      <c r="AE34" s="11"/>
+      <c r="AE34" s="6"/>
     </row>
     <row r="35" spans="1:31">
       <c r="A35" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
       <c r="G35" s="8"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
       <c r="J35" s="9"/>
       <c r="K35" s="9"/>
       <c r="L35" s="9"/>
@@ -3360,17 +3595,17 @@
     </row>
     <row r="36" spans="1:31">
       <c r="A36" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8"/>
-      <c r="I36" s="8"/>
-      <c r="J36" s="9"/>
+        <v>29</v>
+      </c>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11"/>
       <c r="K36" s="9"/>
       <c r="L36" s="9"/>
       <c r="M36" s="8"/>
@@ -3383,56 +3618,1220 @@
       <c r="T36" s="8"/>
       <c r="U36" s="8"/>
       <c r="V36" s="8"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="6"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="6"/>
-      <c r="AB36" s="6"/>
+      <c r="W36" s="11"/>
+      <c r="X36" s="11"/>
+      <c r="Y36" s="11"/>
+      <c r="Z36" s="11"/>
+      <c r="AA36" s="11"/>
+      <c r="AB36" s="11"/>
       <c r="AC36" s="6"/>
       <c r="AD36" s="6"/>
-      <c r="AE36" s="6"/>
-    </row>
-    <row r="37" spans="1:31">
-      <c r="A37" s="1" t="s">
+      <c r="AE36" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="38" spans="1:31" ht="54" customHeight="1">
+      <c r="A38" s="22" t="s">
+        <v>355</v>
+      </c>
+      <c r="B38" s="22"/>
+      <c r="C38" s="22"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="22"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="22"/>
+      <c r="H38" s="22"/>
+      <c r="I38" s="22"/>
+      <c r="J38" s="22"/>
+      <c r="K38" s="22"/>
+      <c r="L38" s="22"/>
+      <c r="M38" s="22"/>
+      <c r="N38" s="22"/>
+      <c r="O38" s="22"/>
+      <c r="P38" s="22"/>
+      <c r="Q38" s="22"/>
+      <c r="R38" s="22"/>
+      <c r="S38" s="22"/>
+      <c r="T38" s="22"/>
+      <c r="U38" s="22"/>
+      <c r="V38" s="22"/>
+      <c r="W38" s="22"/>
+      <c r="X38" s="22"/>
+      <c r="Y38" s="22"/>
+      <c r="Z38" s="22"/>
+      <c r="AA38" s="22"/>
+      <c r="AB38" s="22"/>
+      <c r="AC38" s="22"/>
+      <c r="AD38" s="22"/>
+      <c r="AE38" s="22"/>
+    </row>
+    <row r="39" spans="1:31">
+      <c r="B39" s="15"/>
+      <c r="C39" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="40" spans="1:31">
+      <c r="B40" s="17"/>
+      <c r="C40" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="41" spans="1:31">
+      <c r="B41" s="21"/>
+      <c r="C41" s="2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="43" spans="1:31" ht="91.5" customHeight="1">
+      <c r="A43" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="R43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S43" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="T43" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="U43" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="V43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="W43" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="X43" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y43" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z43" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA43" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB43" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC43" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD43" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE43" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="11"/>
-      <c r="J37" s="11"/>
-      <c r="K37" s="9"/>
-      <c r="L37" s="9"/>
-      <c r="M37" s="8"/>
-      <c r="N37" s="8"/>
-      <c r="O37" s="8"/>
-      <c r="P37" s="8"/>
-      <c r="Q37" s="9"/>
-      <c r="R37" s="9"/>
-      <c r="S37" s="10"/>
-      <c r="T37" s="8"/>
-      <c r="U37" s="8"/>
-      <c r="V37" s="8"/>
-      <c r="W37" s="11"/>
-      <c r="X37" s="11"/>
-      <c r="Y37" s="11"/>
-      <c r="Z37" s="11"/>
-      <c r="AA37" s="11"/>
-      <c r="AB37" s="11"/>
-      <c r="AC37" s="6"/>
-      <c r="AD37" s="6"/>
-      <c r="AE37" s="8" t="s">
-        <v>66</v>
-      </c>
+    </row>
+    <row r="44" spans="1:31">
+      <c r="A44" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B44" s="21"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="21"/>
+      <c r="F44" s="21"/>
+      <c r="G44" s="21"/>
+      <c r="H44" s="21"/>
+      <c r="I44" s="21"/>
+      <c r="J44" s="15"/>
+      <c r="K44" s="15"/>
+      <c r="L44" s="18"/>
+      <c r="M44" s="18"/>
+      <c r="N44" s="18"/>
+      <c r="O44" s="18"/>
+      <c r="P44" s="18"/>
+      <c r="Q44" s="18"/>
+      <c r="R44" s="18"/>
+      <c r="S44" s="16"/>
+      <c r="T44" s="18"/>
+      <c r="U44" s="18"/>
+      <c r="V44" s="18"/>
+      <c r="W44" s="19"/>
+      <c r="X44" s="17"/>
+      <c r="Y44" s="20"/>
+      <c r="Z44" s="19"/>
+      <c r="AA44" s="20"/>
+      <c r="AB44" s="19"/>
+      <c r="AC44" s="19"/>
+      <c r="AD44" s="19"/>
+      <c r="AE44" s="19"/>
+    </row>
+    <row r="45" spans="1:31">
+      <c r="A45" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B45" s="21"/>
+      <c r="C45" s="21"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="21"/>
+      <c r="F45" s="21"/>
+      <c r="G45" s="21"/>
+      <c r="H45" s="21"/>
+      <c r="I45" s="21"/>
+      <c r="J45" s="15"/>
+      <c r="K45" s="15"/>
+      <c r="L45" s="18"/>
+      <c r="M45" s="18"/>
+      <c r="N45" s="18"/>
+      <c r="O45" s="18"/>
+      <c r="P45" s="18"/>
+      <c r="Q45" s="18"/>
+      <c r="R45" s="18"/>
+      <c r="S45" s="16"/>
+      <c r="T45" s="18"/>
+      <c r="U45" s="18"/>
+      <c r="V45" s="18"/>
+      <c r="W45" s="19"/>
+      <c r="X45" s="17"/>
+      <c r="Y45" s="20"/>
+      <c r="Z45" s="19"/>
+      <c r="AA45" s="20"/>
+      <c r="AB45" s="19"/>
+      <c r="AC45" s="19"/>
+      <c r="AD45" s="19"/>
+      <c r="AE45" s="19"/>
+    </row>
+    <row r="46" spans="1:31">
+      <c r="A46" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B46" s="15"/>
+      <c r="C46" s="15"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="21"/>
+      <c r="F46" s="21"/>
+      <c r="G46" s="21"/>
+      <c r="H46" s="21"/>
+      <c r="I46" s="21"/>
+      <c r="J46" s="15"/>
+      <c r="K46" s="15"/>
+      <c r="L46" s="18"/>
+      <c r="M46" s="18"/>
+      <c r="N46" s="18"/>
+      <c r="O46" s="18"/>
+      <c r="P46" s="18"/>
+      <c r="Q46" s="18"/>
+      <c r="R46" s="18"/>
+      <c r="S46" s="16"/>
+      <c r="T46" s="18"/>
+      <c r="U46" s="18"/>
+      <c r="V46" s="18"/>
+      <c r="W46" s="19"/>
+      <c r="X46" s="17"/>
+      <c r="Y46" s="20"/>
+      <c r="Z46" s="19"/>
+      <c r="AA46" s="20"/>
+      <c r="AB46" s="19"/>
+      <c r="AC46" s="19"/>
+      <c r="AD46" s="19"/>
+      <c r="AE46" s="19"/>
+    </row>
+    <row r="47" spans="1:31">
+      <c r="A47" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B47" s="15"/>
+      <c r="C47" s="15"/>
+      <c r="D47" s="18"/>
+      <c r="E47" s="21"/>
+      <c r="F47" s="21"/>
+      <c r="G47" s="21"/>
+      <c r="H47" s="15"/>
+      <c r="I47" s="21"/>
+      <c r="J47" s="15"/>
+      <c r="K47" s="15"/>
+      <c r="L47" s="18"/>
+      <c r="M47" s="18"/>
+      <c r="N47" s="18"/>
+      <c r="O47" s="18"/>
+      <c r="P47" s="18"/>
+      <c r="Q47" s="18"/>
+      <c r="R47" s="18"/>
+      <c r="S47" s="16"/>
+      <c r="T47" s="18"/>
+      <c r="U47" s="18"/>
+      <c r="V47" s="18"/>
+      <c r="W47" s="19"/>
+      <c r="X47" s="17"/>
+      <c r="Y47" s="20"/>
+      <c r="Z47" s="19"/>
+      <c r="AA47" s="20"/>
+      <c r="AB47" s="19"/>
+      <c r="AC47" s="19"/>
+      <c r="AD47" s="19"/>
+      <c r="AE47" s="19"/>
+    </row>
+    <row r="48" spans="1:31">
+      <c r="A48" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B48" s="15"/>
+      <c r="C48" s="15"/>
+      <c r="D48" s="18"/>
+      <c r="E48" s="18"/>
+      <c r="F48" s="21"/>
+      <c r="G48" s="21"/>
+      <c r="H48" s="15"/>
+      <c r="I48" s="21"/>
+      <c r="J48" s="15"/>
+      <c r="K48" s="15"/>
+      <c r="L48" s="18"/>
+      <c r="M48" s="18"/>
+      <c r="N48" s="18"/>
+      <c r="O48" s="18"/>
+      <c r="P48" s="18"/>
+      <c r="Q48" s="18"/>
+      <c r="R48" s="18"/>
+      <c r="S48" s="16"/>
+      <c r="T48" s="18"/>
+      <c r="U48" s="18"/>
+      <c r="V48" s="18"/>
+      <c r="W48" s="19"/>
+      <c r="X48" s="17"/>
+      <c r="Y48" s="20"/>
+      <c r="Z48" s="19"/>
+      <c r="AA48" s="20"/>
+      <c r="AB48" s="19"/>
+      <c r="AC48" s="19"/>
+      <c r="AD48" s="19"/>
+      <c r="AE48" s="19"/>
+    </row>
+    <row r="49" spans="1:31">
+      <c r="A49" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B49" s="15"/>
+      <c r="C49" s="15"/>
+      <c r="D49" s="18"/>
+      <c r="E49" s="18"/>
+      <c r="F49" s="18"/>
+      <c r="G49" s="21"/>
+      <c r="H49" s="15"/>
+      <c r="I49" s="15"/>
+      <c r="J49" s="15"/>
+      <c r="K49" s="15"/>
+      <c r="L49" s="18"/>
+      <c r="M49" s="18"/>
+      <c r="N49" s="18"/>
+      <c r="O49" s="18"/>
+      <c r="P49" s="18"/>
+      <c r="Q49" s="18"/>
+      <c r="R49" s="18"/>
+      <c r="S49" s="16"/>
+      <c r="T49" s="18"/>
+      <c r="U49" s="18"/>
+      <c r="V49" s="18"/>
+      <c r="W49" s="19"/>
+      <c r="X49" s="17"/>
+      <c r="Y49" s="20"/>
+      <c r="Z49" s="19"/>
+      <c r="AA49" s="20"/>
+      <c r="AB49" s="19"/>
+      <c r="AC49" s="19"/>
+      <c r="AD49" s="19"/>
+      <c r="AE49" s="19"/>
+    </row>
+    <row r="50" spans="1:31">
+      <c r="A50" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B50" s="15"/>
+      <c r="C50" s="15"/>
+      <c r="D50" s="18"/>
+      <c r="E50" s="18"/>
+      <c r="F50" s="18"/>
+      <c r="G50" s="18"/>
+      <c r="H50" s="21"/>
+      <c r="I50" s="21"/>
+      <c r="J50" s="15"/>
+      <c r="K50" s="15"/>
+      <c r="L50" s="18"/>
+      <c r="M50" s="18"/>
+      <c r="N50" s="18"/>
+      <c r="O50" s="18"/>
+      <c r="P50" s="18"/>
+      <c r="Q50" s="18"/>
+      <c r="R50" s="18"/>
+      <c r="S50" s="16"/>
+      <c r="T50" s="18"/>
+      <c r="U50" s="18"/>
+      <c r="V50" s="18"/>
+      <c r="W50" s="19"/>
+      <c r="X50" s="17"/>
+      <c r="Y50" s="20"/>
+      <c r="Z50" s="19"/>
+      <c r="AA50" s="20"/>
+      <c r="AB50" s="19"/>
+      <c r="AC50" s="19"/>
+      <c r="AD50" s="19"/>
+      <c r="AE50" s="19"/>
+    </row>
+    <row r="51" spans="1:31">
+      <c r="A51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B51" s="15"/>
+      <c r="C51" s="15"/>
+      <c r="D51" s="18"/>
+      <c r="E51" s="18"/>
+      <c r="F51" s="18"/>
+      <c r="G51" s="18"/>
+      <c r="H51" s="18"/>
+      <c r="I51" s="21"/>
+      <c r="J51" s="15"/>
+      <c r="K51" s="15"/>
+      <c r="L51" s="18"/>
+      <c r="M51" s="18"/>
+      <c r="N51" s="18"/>
+      <c r="O51" s="18"/>
+      <c r="P51" s="18"/>
+      <c r="Q51" s="18"/>
+      <c r="R51" s="18"/>
+      <c r="S51" s="16"/>
+      <c r="T51" s="18"/>
+      <c r="U51" s="18"/>
+      <c r="V51" s="18"/>
+      <c r="W51" s="19"/>
+      <c r="X51" s="17"/>
+      <c r="Y51" s="20"/>
+      <c r="Z51" s="19"/>
+      <c r="AA51" s="20"/>
+      <c r="AB51" s="19"/>
+      <c r="AC51" s="19"/>
+      <c r="AD51" s="19"/>
+      <c r="AE51" s="19"/>
+    </row>
+    <row r="52" spans="1:31">
+      <c r="A52" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B52" s="15"/>
+      <c r="C52" s="15"/>
+      <c r="D52" s="18"/>
+      <c r="E52" s="18"/>
+      <c r="F52" s="18"/>
+      <c r="G52" s="18"/>
+      <c r="H52" s="18"/>
+      <c r="I52" s="18"/>
+      <c r="J52" s="15"/>
+      <c r="K52" s="15"/>
+      <c r="L52" s="18"/>
+      <c r="M52" s="18"/>
+      <c r="N52" s="18"/>
+      <c r="O52" s="18"/>
+      <c r="P52" s="18"/>
+      <c r="Q52" s="18"/>
+      <c r="R52" s="18"/>
+      <c r="S52" s="16"/>
+      <c r="T52" s="18"/>
+      <c r="U52" s="18"/>
+      <c r="V52" s="18"/>
+      <c r="W52" s="19"/>
+      <c r="X52" s="17"/>
+      <c r="Y52" s="20"/>
+      <c r="Z52" s="19"/>
+      <c r="AA52" s="20"/>
+      <c r="AB52" s="19"/>
+      <c r="AC52" s="19"/>
+      <c r="AD52" s="19"/>
+      <c r="AE52" s="19"/>
+    </row>
+    <row r="53" spans="1:31">
+      <c r="A53" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B53" s="15"/>
+      <c r="C53" s="15"/>
+      <c r="D53" s="18"/>
+      <c r="E53" s="18"/>
+      <c r="F53" s="18"/>
+      <c r="G53" s="18"/>
+      <c r="H53" s="18"/>
+      <c r="I53" s="18"/>
+      <c r="J53" s="15"/>
+      <c r="K53" s="15"/>
+      <c r="L53" s="18"/>
+      <c r="M53" s="21"/>
+      <c r="N53" s="21"/>
+      <c r="O53" s="21"/>
+      <c r="P53" s="21"/>
+      <c r="Q53" s="18"/>
+      <c r="R53" s="18"/>
+      <c r="S53" s="16"/>
+      <c r="T53" s="18"/>
+      <c r="U53" s="18"/>
+      <c r="V53" s="18"/>
+      <c r="W53" s="19"/>
+      <c r="X53" s="17"/>
+      <c r="Y53" s="20"/>
+      <c r="Z53" s="19"/>
+      <c r="AA53" s="20"/>
+      <c r="AB53" s="19"/>
+      <c r="AC53" s="20"/>
+      <c r="AD53" s="20"/>
+      <c r="AE53" s="20"/>
+    </row>
+    <row r="54" spans="1:31">
+      <c r="A54" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B54" s="15"/>
+      <c r="C54" s="15"/>
+      <c r="D54" s="18"/>
+      <c r="E54" s="18"/>
+      <c r="F54" s="18"/>
+      <c r="G54" s="18"/>
+      <c r="H54" s="18"/>
+      <c r="I54" s="18"/>
+      <c r="J54" s="15"/>
+      <c r="K54" s="15"/>
+      <c r="L54" s="18"/>
+      <c r="M54" s="21"/>
+      <c r="N54" s="21"/>
+      <c r="O54" s="21"/>
+      <c r="P54" s="21"/>
+      <c r="Q54" s="18"/>
+      <c r="R54" s="18"/>
+      <c r="S54" s="16"/>
+      <c r="T54" s="18"/>
+      <c r="U54" s="18"/>
+      <c r="V54" s="18"/>
+      <c r="W54" s="19"/>
+      <c r="X54" s="17"/>
+      <c r="Y54" s="20"/>
+      <c r="Z54" s="19"/>
+      <c r="AA54" s="20"/>
+      <c r="AB54" s="19"/>
+      <c r="AC54" s="20"/>
+      <c r="AD54" s="20"/>
+      <c r="AE54" s="20"/>
+    </row>
+    <row r="55" spans="1:31">
+      <c r="A55" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B55" s="15"/>
+      <c r="C55" s="15"/>
+      <c r="D55" s="18"/>
+      <c r="E55" s="18"/>
+      <c r="F55" s="18"/>
+      <c r="G55" s="18"/>
+      <c r="H55" s="18"/>
+      <c r="I55" s="18"/>
+      <c r="J55" s="15"/>
+      <c r="K55" s="15"/>
+      <c r="L55" s="18"/>
+      <c r="M55" s="21"/>
+      <c r="N55" s="21"/>
+      <c r="O55" s="21"/>
+      <c r="P55" s="21"/>
+      <c r="Q55" s="18"/>
+      <c r="R55" s="18"/>
+      <c r="S55" s="16"/>
+      <c r="T55" s="18"/>
+      <c r="U55" s="18"/>
+      <c r="V55" s="18"/>
+      <c r="W55" s="19"/>
+      <c r="X55" s="17"/>
+      <c r="Y55" s="20"/>
+      <c r="Z55" s="19"/>
+      <c r="AA55" s="20"/>
+      <c r="AB55" s="19"/>
+      <c r="AC55" s="20"/>
+      <c r="AD55" s="20"/>
+      <c r="AE55" s="20"/>
+    </row>
+    <row r="56" spans="1:31">
+      <c r="A56" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B56" s="15"/>
+      <c r="C56" s="15"/>
+      <c r="D56" s="18"/>
+      <c r="E56" s="18"/>
+      <c r="F56" s="18"/>
+      <c r="G56" s="18"/>
+      <c r="H56" s="18"/>
+      <c r="I56" s="18"/>
+      <c r="J56" s="15"/>
+      <c r="K56" s="15"/>
+      <c r="L56" s="18"/>
+      <c r="M56" s="18"/>
+      <c r="N56" s="21"/>
+      <c r="O56" s="21"/>
+      <c r="P56" s="21"/>
+      <c r="Q56" s="18"/>
+      <c r="R56" s="18"/>
+      <c r="S56" s="16"/>
+      <c r="T56" s="18"/>
+      <c r="U56" s="18"/>
+      <c r="V56" s="18"/>
+      <c r="W56" s="19"/>
+      <c r="X56" s="17"/>
+      <c r="Y56" s="20"/>
+      <c r="Z56" s="19"/>
+      <c r="AA56" s="20"/>
+      <c r="AB56" s="19"/>
+      <c r="AC56" s="20"/>
+      <c r="AD56" s="20"/>
+      <c r="AE56" s="20"/>
+    </row>
+    <row r="57" spans="1:31">
+      <c r="A57" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B57" s="15"/>
+      <c r="C57" s="15"/>
+      <c r="D57" s="18"/>
+      <c r="E57" s="18"/>
+      <c r="F57" s="18"/>
+      <c r="G57" s="18"/>
+      <c r="H57" s="18"/>
+      <c r="I57" s="18"/>
+      <c r="J57" s="15"/>
+      <c r="K57" s="15"/>
+      <c r="L57" s="18"/>
+      <c r="M57" s="18"/>
+      <c r="N57" s="18"/>
+      <c r="O57" s="21"/>
+      <c r="P57" s="21"/>
+      <c r="Q57" s="18"/>
+      <c r="R57" s="18"/>
+      <c r="S57" s="16"/>
+      <c r="T57" s="18"/>
+      <c r="U57" s="18"/>
+      <c r="V57" s="18"/>
+      <c r="W57" s="19"/>
+      <c r="X57" s="17"/>
+      <c r="Y57" s="20"/>
+      <c r="Z57" s="19"/>
+      <c r="AA57" s="20"/>
+      <c r="AB57" s="19"/>
+      <c r="AC57" s="20"/>
+      <c r="AD57" s="20"/>
+      <c r="AE57" s="20"/>
+    </row>
+    <row r="58" spans="1:31">
+      <c r="A58" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B58" s="15"/>
+      <c r="C58" s="15"/>
+      <c r="D58" s="18"/>
+      <c r="E58" s="18"/>
+      <c r="F58" s="18"/>
+      <c r="G58" s="18"/>
+      <c r="H58" s="18"/>
+      <c r="I58" s="18"/>
+      <c r="J58" s="15"/>
+      <c r="K58" s="15"/>
+      <c r="L58" s="18"/>
+      <c r="M58" s="18"/>
+      <c r="N58" s="18"/>
+      <c r="O58" s="18"/>
+      <c r="P58" s="21"/>
+      <c r="Q58" s="18"/>
+      <c r="R58" s="18"/>
+      <c r="S58" s="16"/>
+      <c r="T58" s="18"/>
+      <c r="U58" s="18"/>
+      <c r="V58" s="18"/>
+      <c r="W58" s="19"/>
+      <c r="X58" s="17"/>
+      <c r="Y58" s="20"/>
+      <c r="Z58" s="19"/>
+      <c r="AA58" s="20"/>
+      <c r="AB58" s="19"/>
+      <c r="AC58" s="20"/>
+      <c r="AD58" s="20"/>
+      <c r="AE58" s="20"/>
+    </row>
+    <row r="59" spans="1:31">
+      <c r="A59" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" s="15"/>
+      <c r="C59" s="15"/>
+      <c r="D59" s="18"/>
+      <c r="E59" s="18"/>
+      <c r="F59" s="18"/>
+      <c r="G59" s="18"/>
+      <c r="H59" s="18"/>
+      <c r="I59" s="18"/>
+      <c r="J59" s="15"/>
+      <c r="K59" s="15"/>
+      <c r="L59" s="18"/>
+      <c r="M59" s="18"/>
+      <c r="N59" s="18"/>
+      <c r="O59" s="18"/>
+      <c r="P59" s="15"/>
+      <c r="Q59" s="15"/>
+      <c r="R59" s="18"/>
+      <c r="S59" s="21"/>
+      <c r="T59" s="21"/>
+      <c r="U59" s="21"/>
+      <c r="V59" s="21"/>
+      <c r="W59" s="18"/>
+      <c r="X59" s="17"/>
+      <c r="Y59" s="20"/>
+      <c r="Z59" s="19"/>
+      <c r="AA59" s="20"/>
+      <c r="AB59" s="19"/>
+      <c r="AC59" s="20"/>
+      <c r="AD59" s="20"/>
+      <c r="AE59" s="20"/>
+    </row>
+    <row r="60" spans="1:31">
+      <c r="A60" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B60" s="15"/>
+      <c r="C60" s="15"/>
+      <c r="D60" s="18"/>
+      <c r="E60" s="18"/>
+      <c r="F60" s="18"/>
+      <c r="G60" s="18"/>
+      <c r="H60" s="18"/>
+      <c r="I60" s="18"/>
+      <c r="J60" s="15"/>
+      <c r="K60" s="15"/>
+      <c r="L60" s="18"/>
+      <c r="M60" s="18"/>
+      <c r="N60" s="18"/>
+      <c r="O60" s="18"/>
+      <c r="P60" s="15"/>
+      <c r="Q60" s="15"/>
+      <c r="R60" s="18"/>
+      <c r="S60" s="21"/>
+      <c r="T60" s="21"/>
+      <c r="U60" s="21"/>
+      <c r="V60" s="21"/>
+      <c r="W60" s="18"/>
+      <c r="X60" s="17"/>
+      <c r="Y60" s="20"/>
+      <c r="Z60" s="19"/>
+      <c r="AA60" s="20"/>
+      <c r="AB60" s="19"/>
+      <c r="AC60" s="20"/>
+      <c r="AD60" s="20"/>
+      <c r="AE60" s="20"/>
+    </row>
+    <row r="61" spans="1:31">
+      <c r="A61" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B61" s="15"/>
+      <c r="C61" s="15"/>
+      <c r="D61" s="18"/>
+      <c r="E61" s="18"/>
+      <c r="F61" s="18"/>
+      <c r="G61" s="18"/>
+      <c r="H61" s="18"/>
+      <c r="I61" s="18"/>
+      <c r="J61" s="15"/>
+      <c r="K61" s="15"/>
+      <c r="L61" s="18"/>
+      <c r="M61" s="18"/>
+      <c r="N61" s="18"/>
+      <c r="O61" s="18"/>
+      <c r="P61" s="15"/>
+      <c r="Q61" s="15"/>
+      <c r="R61" s="18"/>
+      <c r="S61" s="21"/>
+      <c r="T61" s="21"/>
+      <c r="U61" s="21"/>
+      <c r="V61" s="21"/>
+      <c r="W61" s="18"/>
+      <c r="X61" s="17"/>
+      <c r="Y61" s="20"/>
+      <c r="Z61" s="19"/>
+      <c r="AA61" s="20"/>
+      <c r="AB61" s="19"/>
+      <c r="AC61" s="20"/>
+      <c r="AD61" s="20"/>
+      <c r="AE61" s="20"/>
+    </row>
+    <row r="62" spans="1:31">
+      <c r="A62" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B62" s="15"/>
+      <c r="C62" s="15"/>
+      <c r="D62" s="18"/>
+      <c r="E62" s="18"/>
+      <c r="F62" s="18"/>
+      <c r="G62" s="18"/>
+      <c r="H62" s="18"/>
+      <c r="I62" s="18"/>
+      <c r="J62" s="15"/>
+      <c r="K62" s="15"/>
+      <c r="L62" s="18"/>
+      <c r="M62" s="18"/>
+      <c r="N62" s="18"/>
+      <c r="O62" s="18"/>
+      <c r="P62" s="15"/>
+      <c r="Q62" s="15"/>
+      <c r="R62" s="18"/>
+      <c r="S62" s="18"/>
+      <c r="T62" s="21"/>
+      <c r="U62" s="21"/>
+      <c r="V62" s="21"/>
+      <c r="W62" s="18"/>
+      <c r="X62" s="17"/>
+      <c r="Y62" s="20"/>
+      <c r="Z62" s="19"/>
+      <c r="AA62" s="20"/>
+      <c r="AB62" s="19"/>
+      <c r="AC62" s="20"/>
+      <c r="AD62" s="20"/>
+      <c r="AE62" s="20"/>
+    </row>
+    <row r="63" spans="1:31">
+      <c r="A63" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B63" s="15"/>
+      <c r="C63" s="15"/>
+      <c r="D63" s="18"/>
+      <c r="E63" s="18"/>
+      <c r="F63" s="18"/>
+      <c r="G63" s="18"/>
+      <c r="H63" s="18"/>
+      <c r="I63" s="18"/>
+      <c r="J63" s="15"/>
+      <c r="K63" s="15"/>
+      <c r="L63" s="18"/>
+      <c r="M63" s="18"/>
+      <c r="N63" s="18"/>
+      <c r="O63" s="18"/>
+      <c r="P63" s="15"/>
+      <c r="Q63" s="15"/>
+      <c r="R63" s="18"/>
+      <c r="S63" s="18"/>
+      <c r="T63" s="18"/>
+      <c r="U63" s="21"/>
+      <c r="V63" s="21"/>
+      <c r="W63" s="18"/>
+      <c r="X63" s="17"/>
+      <c r="Y63" s="20"/>
+      <c r="Z63" s="19"/>
+      <c r="AA63" s="20"/>
+      <c r="AB63" s="19"/>
+      <c r="AC63" s="20"/>
+      <c r="AD63" s="20"/>
+      <c r="AE63" s="20"/>
+    </row>
+    <row r="64" spans="1:31">
+      <c r="A64" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B64" s="15"/>
+      <c r="C64" s="15"/>
+      <c r="D64" s="18"/>
+      <c r="E64" s="18"/>
+      <c r="F64" s="18"/>
+      <c r="G64" s="18"/>
+      <c r="H64" s="18"/>
+      <c r="I64" s="18"/>
+      <c r="J64" s="15"/>
+      <c r="K64" s="15"/>
+      <c r="L64" s="18"/>
+      <c r="M64" s="18"/>
+      <c r="N64" s="18"/>
+      <c r="O64" s="18"/>
+      <c r="P64" s="15"/>
+      <c r="Q64" s="15"/>
+      <c r="R64" s="18"/>
+      <c r="S64" s="18"/>
+      <c r="T64" s="18"/>
+      <c r="U64" s="18"/>
+      <c r="V64" s="21"/>
+      <c r="W64" s="18"/>
+      <c r="X64" s="17"/>
+      <c r="Y64" s="20"/>
+      <c r="Z64" s="19"/>
+      <c r="AA64" s="20"/>
+      <c r="AB64" s="19"/>
+      <c r="AC64" s="20"/>
+      <c r="AD64" s="20"/>
+      <c r="AE64" s="20"/>
+    </row>
+    <row r="65" spans="1:31">
+      <c r="A65" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B65" s="15"/>
+      <c r="C65" s="15"/>
+      <c r="D65" s="18"/>
+      <c r="E65" s="18"/>
+      <c r="F65" s="18"/>
+      <c r="G65" s="18"/>
+      <c r="H65" s="18"/>
+      <c r="I65" s="18"/>
+      <c r="J65" s="15"/>
+      <c r="K65" s="15"/>
+      <c r="L65" s="18"/>
+      <c r="M65" s="18"/>
+      <c r="N65" s="18"/>
+      <c r="O65" s="18"/>
+      <c r="P65" s="18"/>
+      <c r="Q65" s="18"/>
+      <c r="R65" s="18"/>
+      <c r="S65" s="16"/>
+      <c r="T65" s="18"/>
+      <c r="U65" s="18"/>
+      <c r="V65" s="18"/>
+      <c r="W65" s="19"/>
+      <c r="X65" s="17"/>
+      <c r="Y65" s="20"/>
+      <c r="Z65" s="20"/>
+      <c r="AA65" s="20"/>
+      <c r="AB65" s="20"/>
+      <c r="AC65" s="19"/>
+      <c r="AD65" s="19"/>
+      <c r="AE65" s="19"/>
+    </row>
+    <row r="66" spans="1:31">
+      <c r="A66" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B66" s="15"/>
+      <c r="C66" s="15"/>
+      <c r="D66" s="21"/>
+      <c r="E66" s="21"/>
+      <c r="F66" s="21"/>
+      <c r="G66" s="21"/>
+      <c r="H66" s="21"/>
+      <c r="I66" s="21"/>
+      <c r="J66" s="15"/>
+      <c r="K66" s="15"/>
+      <c r="L66" s="18"/>
+      <c r="M66" s="18"/>
+      <c r="N66" s="18"/>
+      <c r="O66" s="18"/>
+      <c r="P66" s="18"/>
+      <c r="Q66" s="18"/>
+      <c r="R66" s="18"/>
+      <c r="S66" s="16"/>
+      <c r="T66" s="18"/>
+      <c r="U66" s="18"/>
+      <c r="V66" s="18"/>
+      <c r="W66" s="19"/>
+      <c r="X66" s="21"/>
+      <c r="Y66" s="20"/>
+      <c r="Z66" s="20"/>
+      <c r="AA66" s="20"/>
+      <c r="AB66" s="20"/>
+      <c r="AC66" s="19"/>
+      <c r="AD66" s="19"/>
+      <c r="AE66" s="19"/>
+    </row>
+    <row r="67" spans="1:31">
+      <c r="A67" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B67" s="15"/>
+      <c r="C67" s="15"/>
+      <c r="D67" s="18"/>
+      <c r="E67" s="18"/>
+      <c r="F67" s="18"/>
+      <c r="G67" s="18"/>
+      <c r="H67" s="18"/>
+      <c r="I67" s="21"/>
+      <c r="J67" s="17"/>
+      <c r="K67" s="20"/>
+      <c r="L67" s="20"/>
+      <c r="M67" s="20"/>
+      <c r="N67" s="20"/>
+      <c r="O67" s="17"/>
+      <c r="P67" s="20"/>
+      <c r="Q67" s="20"/>
+      <c r="R67" s="20"/>
+      <c r="S67" s="20"/>
+      <c r="T67" s="20"/>
+      <c r="U67" s="20"/>
+      <c r="V67" s="20"/>
+      <c r="W67" s="19"/>
+      <c r="X67" s="17"/>
+      <c r="Y67" s="20"/>
+      <c r="Z67" s="20"/>
+      <c r="AA67" s="20"/>
+      <c r="AB67" s="20"/>
+      <c r="AC67" s="19"/>
+      <c r="AD67" s="19"/>
+      <c r="AE67" s="19"/>
+    </row>
+    <row r="68" spans="1:31">
+      <c r="A68" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B68" s="15"/>
+      <c r="C68" s="15"/>
+      <c r="D68" s="18"/>
+      <c r="E68" s="18"/>
+      <c r="F68" s="18"/>
+      <c r="G68" s="18"/>
+      <c r="H68" s="18"/>
+      <c r="I68" s="18"/>
+      <c r="J68" s="15"/>
+      <c r="K68" s="15"/>
+      <c r="L68" s="18"/>
+      <c r="M68" s="18"/>
+      <c r="N68" s="18"/>
+      <c r="O68" s="18"/>
+      <c r="P68" s="18"/>
+      <c r="Q68" s="18"/>
+      <c r="R68" s="18"/>
+      <c r="S68" s="16"/>
+      <c r="T68" s="18"/>
+      <c r="U68" s="18"/>
+      <c r="V68" s="18"/>
+      <c r="W68" s="19"/>
+      <c r="X68" s="19"/>
+      <c r="Y68" s="19"/>
+      <c r="Z68" s="21"/>
+      <c r="AA68" s="20"/>
+      <c r="AB68" s="19"/>
+      <c r="AC68" s="19"/>
+      <c r="AD68" s="19"/>
+      <c r="AE68" s="19"/>
+    </row>
+    <row r="69" spans="1:31">
+      <c r="A69" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B69" s="20"/>
+      <c r="C69" s="20"/>
+      <c r="D69" s="20"/>
+      <c r="E69" s="20"/>
+      <c r="F69" s="17"/>
+      <c r="G69" s="20"/>
+      <c r="H69" s="20"/>
+      <c r="I69" s="20"/>
+      <c r="J69" s="20"/>
+      <c r="K69" s="15"/>
+      <c r="L69" s="18"/>
+      <c r="M69" s="18"/>
+      <c r="N69" s="18"/>
+      <c r="O69" s="18"/>
+      <c r="P69" s="18"/>
+      <c r="Q69" s="18"/>
+      <c r="R69" s="18"/>
+      <c r="S69" s="16"/>
+      <c r="T69" s="18"/>
+      <c r="U69" s="18"/>
+      <c r="V69" s="18"/>
+      <c r="W69" s="17"/>
+      <c r="X69" s="20"/>
+      <c r="Y69" s="20"/>
+      <c r="Z69" s="20"/>
+      <c r="AA69" s="20"/>
+      <c r="AB69" s="19"/>
+      <c r="AC69" s="20"/>
+      <c r="AD69" s="20"/>
+      <c r="AE69" s="19"/>
+    </row>
+    <row r="70" spans="1:31">
+      <c r="A70" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B70" s="15"/>
+      <c r="C70" s="15"/>
+      <c r="D70" s="18"/>
+      <c r="E70" s="18"/>
+      <c r="F70" s="18"/>
+      <c r="G70" s="18"/>
+      <c r="H70" s="18"/>
+      <c r="I70" s="18"/>
+      <c r="J70" s="15"/>
+      <c r="K70" s="15"/>
+      <c r="L70" s="18"/>
+      <c r="M70" s="18"/>
+      <c r="N70" s="18"/>
+      <c r="O70" s="18"/>
+      <c r="P70" s="18"/>
+      <c r="Q70" s="18"/>
+      <c r="R70" s="18"/>
+      <c r="S70" s="16"/>
+      <c r="T70" s="18"/>
+      <c r="U70" s="18"/>
+      <c r="V70" s="18"/>
+      <c r="W70" s="19"/>
+      <c r="X70" s="20"/>
+      <c r="Y70" s="20"/>
+      <c r="Z70" s="19"/>
+      <c r="AA70" s="20"/>
+      <c r="AB70" s="19"/>
+      <c r="AC70" s="19"/>
+      <c r="AD70" s="19"/>
+      <c r="AE70" s="19"/>
+    </row>
+    <row r="71" spans="1:31">
+      <c r="A71" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B71" s="15"/>
+      <c r="C71" s="15"/>
+      <c r="D71" s="18"/>
+      <c r="E71" s="18"/>
+      <c r="F71" s="18"/>
+      <c r="G71" s="18"/>
+      <c r="H71" s="18"/>
+      <c r="I71" s="18"/>
+      <c r="J71" s="15"/>
+      <c r="K71" s="20"/>
+      <c r="L71" s="20"/>
+      <c r="M71" s="20"/>
+      <c r="N71" s="20"/>
+      <c r="O71" s="17"/>
+      <c r="P71" s="20"/>
+      <c r="Q71" s="20"/>
+      <c r="R71" s="20"/>
+      <c r="S71" s="20"/>
+      <c r="T71" s="20"/>
+      <c r="U71" s="20"/>
+      <c r="V71" s="20"/>
+      <c r="W71" s="19"/>
+      <c r="X71" s="17"/>
+      <c r="Y71" s="20"/>
+      <c r="Z71" s="20"/>
+      <c r="AA71" s="20"/>
+      <c r="AB71" s="20"/>
+      <c r="AC71" s="20"/>
+      <c r="AD71" s="20"/>
+      <c r="AE71" s="20"/>
+    </row>
+    <row r="72" spans="1:31">
+      <c r="A72" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B72" s="15"/>
+      <c r="C72" s="15"/>
+      <c r="D72" s="18"/>
+      <c r="E72" s="18"/>
+      <c r="F72" s="18"/>
+      <c r="G72" s="18"/>
+      <c r="H72" s="18"/>
+      <c r="I72" s="18"/>
+      <c r="J72" s="15"/>
+      <c r="K72" s="20"/>
+      <c r="L72" s="20"/>
+      <c r="M72" s="20"/>
+      <c r="N72" s="20"/>
+      <c r="O72" s="17"/>
+      <c r="P72" s="20"/>
+      <c r="Q72" s="20"/>
+      <c r="R72" s="20"/>
+      <c r="S72" s="20"/>
+      <c r="T72" s="20"/>
+      <c r="U72" s="20"/>
+      <c r="V72" s="20"/>
+      <c r="W72" s="19"/>
+      <c r="X72" s="17"/>
+      <c r="Y72" s="20"/>
+      <c r="Z72" s="20"/>
+      <c r="AA72" s="20"/>
+      <c r="AB72" s="20"/>
+      <c r="AC72" s="20"/>
+      <c r="AD72" s="20"/>
+      <c r="AE72" s="20"/>
+    </row>
+    <row r="73" spans="1:31">
+      <c r="A73" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B73" s="15"/>
+      <c r="C73" s="15"/>
+      <c r="D73" s="18"/>
+      <c r="E73" s="18"/>
+      <c r="F73" s="18"/>
+      <c r="G73" s="18"/>
+      <c r="H73" s="18"/>
+      <c r="I73" s="18"/>
+      <c r="J73" s="15"/>
+      <c r="K73" s="20"/>
+      <c r="L73" s="20"/>
+      <c r="M73" s="20"/>
+      <c r="N73" s="20"/>
+      <c r="O73" s="17"/>
+      <c r="P73" s="20"/>
+      <c r="Q73" s="18"/>
+      <c r="R73" s="18"/>
+      <c r="S73" s="16"/>
+      <c r="T73" s="18"/>
+      <c r="U73" s="18"/>
+      <c r="V73" s="18"/>
+      <c r="W73" s="18"/>
+      <c r="X73" s="18"/>
+      <c r="Y73" s="16"/>
+      <c r="Z73" s="18"/>
+      <c r="AA73" s="18"/>
+      <c r="AB73" s="18"/>
+      <c r="AC73" s="20"/>
+      <c r="AD73" s="20"/>
+      <c r="AE73" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:AE1"/>
+    <mergeCell ref="A38:AE38"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3442,7 +4841,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="29.375" customWidth="1"/>
@@ -3450,116 +4849,217 @@
   <sheetData>
     <row r="1" spans="1:2" s="12" customFormat="1">
       <c r="A1" s="12" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
     </row>
     <row r="15" spans="1:2" s="12" customFormat="1">
       <c r="A15" s="12" t="s">
-        <v>210</v>
+        <v>350</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="14" t="s">
-        <v>292</v>
-      </c>
-      <c r="B16" t="s">
-        <v>293</v>
+      <c r="A16" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" s="12" customFormat="1">
+      <c r="A29" s="12" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="B30" t="s">
+        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -3570,7 +5070,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="29.375" customWidth="1"/>
@@ -3578,116 +5078,217 @@
   <sheetData>
     <row r="1" spans="1:2" s="12" customFormat="1">
       <c r="A1" s="12" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>342</v>
+        <v>396</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
     </row>
     <row r="15" spans="1:2" s="12" customFormat="1">
       <c r="A15" s="12" t="s">
-        <v>210</v>
+        <v>350</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="14" t="s">
-        <v>340</v>
-      </c>
-      <c r="B16" t="s">
-        <v>344</v>
+      <c r="A16" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" s="12" customFormat="1">
+      <c r="A29" s="12" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="14" t="s">
+        <v>335</v>
+      </c>
+      <c r="B30" t="s">
+        <v>338</v>
       </c>
     </row>
   </sheetData>
@@ -3698,7 +5299,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="29.375" customWidth="1"/>
@@ -3706,116 +5307,217 @@
   <sheetData>
     <row r="1" spans="1:2" s="12" customFormat="1">
       <c r="A1" s="12" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
     </row>
     <row r="15" spans="1:2" s="12" customFormat="1">
       <c r="A15" s="12" t="s">
-        <v>210</v>
+        <v>350</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="14" t="s">
-        <v>339</v>
-      </c>
-      <c r="B16" t="s">
-        <v>343</v>
+      <c r="A16" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" s="12" customFormat="1">
+      <c r="A29" s="12" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="14" t="s">
+        <v>334</v>
+      </c>
+      <c r="B30" t="s">
+        <v>337</v>
       </c>
     </row>
   </sheetData>
@@ -3826,7 +5528,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="29.375" customWidth="1"/>
@@ -3834,116 +5536,217 @@
   <sheetData>
     <row r="1" spans="1:2" s="12" customFormat="1">
       <c r="A1" s="12" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15" spans="1:2" s="12" customFormat="1">
       <c r="A15" s="12" t="s">
-        <v>210</v>
+        <v>350</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="14" t="s">
-        <v>351</v>
-      </c>
-      <c r="B16" t="s">
-        <v>352</v>
+      <c r="A16" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" s="12" customFormat="1">
+      <c r="A29" s="12" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="14" t="s">
+        <v>344</v>
+      </c>
+      <c r="B30" t="s">
+        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -3954,7 +5757,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" customWidth="1"/>
@@ -3962,7 +5765,7 @@
   <sheetData>
     <row r="1" spans="1:2" s="12" customFormat="1">
       <c r="A1" s="12" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -3970,7 +5773,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3978,12 +5781,12 @@
         <v>38</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>61</v>
+        <v>352</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="7" t="s">
-        <v>34</v>
+        <v>351</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>60</v>
@@ -4002,7 +5805,7 @@
         <v>34</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -4042,7 +5845,7 @@
         <v>44</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -4050,7 +5853,7 @@
         <v>45</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -4066,7 +5869,7 @@
         <v>48</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -4074,7 +5877,7 @@
         <v>49</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -4082,7 +5885,7 @@
         <v>50</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -4090,7 +5893,7 @@
         <v>51</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -4098,7 +5901,7 @@
         <v>52</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -4111,90 +5914,240 @@
     </row>
     <row r="21" spans="1:2" s="12" customFormat="1">
       <c r="A21" s="12" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" s="12" customFormat="1">
+      <c r="A41" s="12" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" t="s">
+      <c r="B42" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>213</v>
+      </c>
+      <c r="B43" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
         <v>214</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B44" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" t="s">
+        <v>215</v>
+      </c>
+      <c r="B45" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>216</v>
+      </c>
+      <c r="B46" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>217</v>
+      </c>
+      <c r="B47" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
-      <c r="A23" t="s">
-        <v>217</v>
-      </c>
-      <c r="B23" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" t="s">
+    <row r="48" spans="1:2">
+      <c r="A48" t="s">
+        <v>211</v>
+      </c>
+      <c r="B48" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>212</v>
+      </c>
+      <c r="B49" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" t="s">
         <v>218</v>
       </c>
-      <c r="B24" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" t="s">
-        <v>219</v>
-      </c>
-      <c r="B25" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" t="s">
-        <v>220</v>
-      </c>
-      <c r="B26" t="s">
+      <c r="B50" t="s">
         <v>227</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" t="s">
-        <v>221</v>
-      </c>
-      <c r="B27" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" t="s">
-        <v>215</v>
-      </c>
-      <c r="B28" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" t="s">
-        <v>216</v>
-      </c>
-      <c r="B29" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" t="s">
-        <v>222</v>
-      </c>
-      <c r="B30" t="s">
-        <v>231</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="25.125" customWidth="1"/>
@@ -4202,7 +6155,7 @@
   <sheetData>
     <row r="1" spans="1:2" s="12" customFormat="1">
       <c r="A1" s="12" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -4218,15 +6171,15 @@
         <v>59</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -4239,119 +6192,220 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>70</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>80</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:2" s="12" customFormat="1">
       <c r="A15" s="12" t="s">
-        <v>210</v>
+        <v>350</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>250</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="A16" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" s="12" customFormat="1">
+      <c r="A29" s="12" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>246</v>
+      </c>
+      <c r="B30" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>247</v>
+      </c>
+      <c r="B31" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>229</v>
+      </c>
+      <c r="B32" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>228</v>
+      </c>
+      <c r="B33" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>230</v>
+      </c>
+      <c r="B34" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>231</v>
+      </c>
+      <c r="B35" t="s">
         <v>236</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
-        <v>251</v>
-      </c>
-      <c r="B17" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" t="s">
-        <v>233</v>
-      </c>
-      <c r="B18" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
-        <v>232</v>
-      </c>
-      <c r="B19" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" t="s">
-        <v>234</v>
-      </c>
-      <c r="B20" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" t="s">
-        <v>235</v>
-      </c>
-      <c r="B21" t="s">
-        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -4362,7 +6416,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="24.75" customWidth="1"/>
@@ -4370,156 +6424,257 @@
   <sheetData>
     <row r="1" spans="1:2" s="12" customFormat="1">
       <c r="A1" s="12" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>94</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" spans="1:2" s="12" customFormat="1">
       <c r="A15" s="12" t="s">
-        <v>210</v>
+        <v>350</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" t="s">
+      <c r="A16" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" s="12" customFormat="1">
+      <c r="A29" s="12" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>248</v>
+      </c>
+      <c r="B30" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>249</v>
+      </c>
+      <c r="B31" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>237</v>
+      </c>
+      <c r="B32" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>238</v>
+      </c>
+      <c r="B33" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>239</v>
+      </c>
+      <c r="B34" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>240</v>
+      </c>
+      <c r="B35" t="s">
         <v>252</v>
-      </c>
-      <c r="B16" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
-        <v>253</v>
-      </c>
-      <c r="B17" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" t="s">
-        <v>241</v>
-      </c>
-      <c r="B18" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
-        <v>242</v>
-      </c>
-      <c r="B19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" t="s">
-        <v>243</v>
-      </c>
-      <c r="B20" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" t="s">
-        <v>244</v>
-      </c>
-      <c r="B21" t="s">
-        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -4530,7 +6685,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -4538,127 +6693,229 @@
   <sheetData>
     <row r="1" spans="1:2" s="12" customFormat="1">
       <c r="A1" s="12" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:2" s="12" customFormat="1">
       <c r="A15" s="12" t="s">
-        <v>210</v>
+        <v>350</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>254</v>
-      </c>
-      <c r="B16" t="s">
-        <v>249</v>
+      <c r="A16" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" s="12" customFormat="1">
+      <c r="A29" s="12" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>250</v>
+      </c>
+      <c r="B30" t="s">
+        <v>245</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.5" customWidth="1"/>
@@ -4666,116 +6923,217 @@
   <sheetData>
     <row r="1" spans="1:2" s="12" customFormat="1">
       <c r="A1" s="12" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>153</v>
+        <v>384</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>154</v>
+        <v>383</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15" spans="1:2" s="12" customFormat="1">
       <c r="A15" s="12" t="s">
-        <v>210</v>
+        <v>350</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>255</v>
-      </c>
-      <c r="B16" t="s">
-        <v>272</v>
+      <c r="A16" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" s="12" customFormat="1">
+      <c r="A29" s="12" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>251</v>
+      </c>
+      <c r="B30" t="s">
+        <v>399</v>
       </c>
     </row>
   </sheetData>
@@ -4786,7 +7144,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="23.625" customWidth="1"/>
@@ -4794,116 +7152,217 @@
   <sheetData>
     <row r="1" spans="1:2" s="12" customFormat="1">
       <c r="A1" s="12" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>203</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15" spans="1:2" s="12" customFormat="1">
       <c r="A15" s="12" t="s">
-        <v>210</v>
+        <v>350</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>257</v>
-      </c>
-      <c r="B16" t="s">
-        <v>258</v>
+      <c r="A16" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" s="12" customFormat="1">
+      <c r="A29" s="12" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>253</v>
+      </c>
+      <c r="B30" t="s">
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -4914,7 +7373,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="23.75" customWidth="1"/>
@@ -4922,116 +7381,217 @@
   <sheetData>
     <row r="1" spans="1:2" s="12" customFormat="1">
       <c r="A1" s="12" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:2" s="12" customFormat="1">
       <c r="A15" s="12" t="s">
-        <v>210</v>
+        <v>350</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>273</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>274</v>
+      <c r="A16" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" s="12" customFormat="1">
+      <c r="A29" s="12" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>268</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>269</v>
       </c>
     </row>
   </sheetData>
@@ -5042,7 +7602,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="27.875" customWidth="1"/>
@@ -5050,116 +7610,217 @@
   <sheetData>
     <row r="1" spans="1:2" s="12" customFormat="1">
       <c r="A1" s="12" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
     </row>
     <row r="15" spans="1:2" s="12" customFormat="1">
       <c r="A15" s="12" t="s">
-        <v>210</v>
+        <v>350</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>287</v>
-      </c>
-      <c r="B16" t="s">
-        <v>288</v>
+      <c r="A16" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" s="12" customFormat="1">
+      <c r="A29" s="12" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>282</v>
+      </c>
+      <c r="B30" t="s">
+        <v>283</v>
       </c>
     </row>
   </sheetData>
